--- a/output/pdf_financials_xlsx/BPAI.xlsx
+++ b/output/pdf_financials_xlsx/BPAI.xlsx
@@ -469,15 +469,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0.464372</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.398023</v>
       </c>
     </row>
     <row r="5">
@@ -512,15 +508,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.916655</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1.49201</v>
       </c>
     </row>
     <row r="8">
@@ -542,15 +534,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -559,15 +547,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>-2.139707</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-2.700958</v>
       </c>
     </row>
     <row r="11">
@@ -576,15 +560,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-1.943032</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-2.443094</v>
       </c>
     </row>
     <row r="12">
@@ -593,15 +573,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -610,15 +586,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -627,15 +599,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -644,15 +612,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -661,15 +625,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-2.027672</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-2.602701</v>
       </c>
     </row>
     <row r="17">
@@ -678,15 +638,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -729,15 +685,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-2.027672</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-2.602701</v>
       </c>
     </row>
     <row r="21">
@@ -746,15 +698,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -763,15 +711,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -780,15 +724,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-2.027672</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-2.602701</v>
       </c>
     </row>
     <row r="24">
@@ -848,15 +788,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-2.027672</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-2.602701</v>
       </c>
     </row>
     <row r="28">
@@ -865,15 +801,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -882,15 +814,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-2.027672</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-2.602701</v>
       </c>
     </row>
     <row r="30">
@@ -899,15 +827,11 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>-436.6482044567717</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-653.9071862681302</v>
       </c>
     </row>
     <row r="31">
@@ -916,15 +840,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -933,15 +853,11 @@
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>-436.6482044567717</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-653.9071862681302</v>
       </c>
     </row>
     <row r="33">
@@ -970,15 +886,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -987,15 +899,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.093861</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0.433801</v>
       </c>
     </row>
     <row r="37">
@@ -1017,15 +925,11 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1034,15 +938,11 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1051,15 +951,11 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1068,15 +964,11 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.053287</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.139371</v>
       </c>
     </row>
     <row r="42">
@@ -1085,15 +977,11 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1102,15 +990,11 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1119,15 +1003,11 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1136,15 +1016,11 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1153,15 +1029,11 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1170,15 +1042,11 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1187,15 +1055,11 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.040808</v>
       </c>
     </row>
     <row r="49">
@@ -1217,15 +1081,11 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1234,15 +1094,11 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1251,15 +1107,11 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1268,15 +1120,11 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1285,15 +1133,11 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1319,15 +1163,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1336,15 +1176,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1353,15 +1189,11 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1370,15 +1202,11 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1387,15 +1215,11 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1404,15 +1228,11 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0.04517</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.021375</v>
       </c>
     </row>
     <row r="62">
@@ -1421,15 +1241,11 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>0.04517</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0.021375</v>
       </c>
     </row>
     <row r="63">
@@ -1451,15 +1267,11 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1468,15 +1280,11 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1485,15 +1293,11 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1502,15 +1306,11 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1532,15 +1332,11 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1549,15 +1345,11 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1566,15 +1358,11 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1596,15 +1384,11 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1613,15 +1397,11 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0.09457400000000001</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0.025573</v>
       </c>
     </row>
     <row r="75">
@@ -1630,15 +1410,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0.253536</v>
       </c>
     </row>
     <row r="76">
@@ -1660,15 +1436,11 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1677,15 +1449,11 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1694,15 +1462,11 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1711,10 +1475,8 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>-0.1279513252686466</v>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
@@ -1728,15 +1490,11 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1745,15 +1503,11 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1762,15 +1516,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1779,15 +1529,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1796,15 +1542,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0.424843</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0.15962</v>
       </c>
     </row>
     <row r="86">
@@ -1813,15 +1555,11 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>0.424843</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0.15962</v>
       </c>
     </row>
     <row r="87">
@@ -1843,15 +1581,11 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>2.987385</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>5.882081</v>
       </c>
     </row>
     <row r="89">
@@ -1860,15 +1594,11 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1890,15 +1620,11 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1907,15 +1633,11 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1924,15 +1646,11 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1941,15 +1659,11 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>-1.953868</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>-0.533149</v>
       </c>
     </row>
     <row r="95">
@@ -1958,15 +1672,11 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2008,15 +1718,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-2.027672</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-2.602701</v>
       </c>
     </row>
     <row r="100">
@@ -2025,15 +1731,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2055,15 +1757,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2072,15 +1770,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.036728</v>
       </c>
     </row>
     <row r="104">
@@ -2102,15 +1796,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>-0.032915</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>-0.06900100000000001</v>
       </c>
     </row>
     <row r="106">
@@ -2119,15 +1809,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.683657</v>
       </c>
     </row>
     <row r="107">
@@ -2149,15 +1835,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2166,15 +1848,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2183,15 +1861,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2200,15 +1874,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2217,15 +1887,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2234,15 +1900,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2251,15 +1913,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2268,15 +1926,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2285,15 +1939,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2302,15 +1952,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2319,15 +1965,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2336,10 +1978,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0.469201</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>1.964456</v>
@@ -2351,15 +1991,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2368,15 +2004,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2385,15 +2017,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2402,15 +2030,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2419,15 +2043,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2436,15 +2056,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2453,15 +2069,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2487,15 +2099,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="129">
@@ -2504,15 +2112,11 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>1.251529</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>1.206625</v>
       </c>
     </row>
     <row r="130">
@@ -2534,15 +2138,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2551,15 +2151,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.050987</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0.33994</v>
       </c>
     </row>
     <row r="133">
@@ -2568,15 +2164,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.093861</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.433801</v>
       </c>
     </row>
     <row r="134">
@@ -2585,15 +2177,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2602,15 +2190,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-1.669743</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-2.147484</v>
       </c>
     </row>
   </sheetData>
@@ -2927,7 +2511,11 @@
           <t>Loan payable</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>0.25</v>
       </c>
@@ -3267,7 +2855,11 @@
           <t>Net loss for the year</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>-2.027672</v>
       </c>
@@ -3443,7 +3035,11 @@
           <t>Operating Activities total</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>-1.669743</v>
       </c>
@@ -3495,7 +3091,11 @@
           <t>Prepaid expenses</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -3521,7 +3121,11 @@
           <t>Deferred revenue</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangeInOtherWorkingCapital</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>-0.032915</v>
       </c>
@@ -3651,7 +3255,11 @@
           <t>Share issue costs</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -3853,7 +3461,11 @@
           <t>Cash Flows provided by Financing Activities</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>1.251529</v>
       </c>
@@ -3933,7 +3545,11 @@
           <t>Increase in cash</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>0.050987</v>
       </c>
@@ -3985,7 +3601,11 @@
           <t>Cash, end of the year</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>0.093861</v>
       </c>
@@ -4421,7 +4041,11 @@
           <t>Net loss for the year - - - - - -</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>-2.027672</v>
       </c>
@@ -4677,7 +4301,11 @@
           <t>Sales revenue</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>0.464372</v>
       </c>
@@ -4757,7 +4385,11 @@
           <t>Salaries and consulting fees</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>0.793075</v>
       </c>
@@ -4861,7 +4493,11 @@
           <t>Office and general</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
         <v>0.12358</v>
       </c>
@@ -4961,7 +4597,11 @@
           <t>Expenses total</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>-2.139707</v>
       </c>
@@ -4985,7 +4625,11 @@
           <t>Loss before Other Income/(Expenses)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
         <v>-1.943032</v>
       </c>
@@ -5133,7 +4777,11 @@
           <t>Other Income (Expenses) total</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="n">
         <v>-0.08464000000000001</v>
       </c>
@@ -5213,7 +4861,11 @@
           <t>Net Loss and Comprehensive Loss</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>-2.027672</v>
       </c>

--- a/output/pdf_financials_xlsx/BPAI.xlsx
+++ b/output/pdf_financials_xlsx/BPAI.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/BPAI.xlsx
+++ b/output/pdf_financials_xlsx/BPAI.xlsx
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.267697</v>
+        <v>0.267697</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-0.140159</v>
+        <v>0.140159</v>
       </c>
     </row>
     <row r="6">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-2.139707</v>
+        <v>2.139707</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-2.700958</v>
+        <v>2.700958</v>
       </c>
     </row>
     <row r="11">
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2134,7 +2134,7 @@
         <v>0.042874</v>
       </c>
       <c r="C130" s="3" t="n">
-        <v>1e-06</v>
+        <v>0.093861</v>
       </c>
     </row>
     <row r="131">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year 1,9499,038,876</t>
+          <t>Cash, beginning of the year</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3587,7 +3587,7 @@
         <v>0.042874</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.093861</v>
       </c>
     </row>
     <row r="52">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>-0.267697</v>
+        <v>0.267697</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>-0.140159</v>
+        <v>0.140159</v>
       </c>
     </row>
     <row r="81">
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>-2.139707</v>
+        <v>2.139707</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-2.700958</v>
+        <v>2.700958</v>
       </c>
     </row>
     <row r="91">
@@ -4788,10 +4788,10 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>-0.08464000000000001</v>
+        <v>0.08464000000000001</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>-0.159607</v>
+        <v>0.159607</v>
       </c>
     </row>
     <row r="98">

--- a/output/pdf_financials_xlsx/BPAI.xlsx
+++ b/output/pdf_financials_xlsx/BPAI.xlsx
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.330995</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.177538</v>
       </c>
     </row>
     <row r="93">
@@ -2752,7 +2752,11 @@
           <t>Reserve for Warrants (Note 12)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>1.330995</v>
       </c>
